--- a/HGA/filter smh.xlsx
+++ b/HGA/filter smh.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD HGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B376F052-1514-4F27-A46B-89D254A963D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39899060-5C36-4FA7-95F0-C64A637CF2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA9E0192-5E03-49CC-971F-E04A0DCED2FF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>SMH</t>
   </si>
@@ -56,18 +56,6 @@
     <t>PCX 160</t>
   </si>
   <si>
-    <t>PCX 160 ROADSYNC</t>
-  </si>
-  <si>
-    <t>SCOOPY LIME GREEN</t>
-  </si>
-  <si>
-    <t>SCOOPY ORANGE</t>
-  </si>
-  <si>
-    <t>SCOOPY SILVER</t>
-  </si>
-  <si>
     <t>STYLO 160</t>
   </si>
   <si>
@@ -77,10 +65,7 @@
     <t>VARIO 160</t>
   </si>
   <si>
-    <t>2025 ADV 160</t>
-  </si>
-  <si>
-    <t>2025 VARIO 125</t>
+    <t>SCOOPY</t>
   </si>
 </sst>
 </file>
@@ -136,8 +121,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{12048F64-9767-4EC6-B956-9380F61C03FD}" name="FilterSMH" displayName="FilterSMH" ref="A1:A15" totalsRowShown="0">
-  <autoFilter ref="A1:A15" xr:uid="{12048F64-9767-4EC6-B956-9380F61C03FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{12048F64-9767-4EC6-B956-9380F61C03FD}" name="FilterSMH" displayName="FilterSMH" ref="A1:A10" totalsRowShown="0">
+  <autoFilter ref="A1:A10" xr:uid="{12048F64-9767-4EC6-B956-9380F61C03FD}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{1C8D5F6B-37E1-44C6-AAFE-7068A1BAC055}" name="SMH"/>
   </tableColumns>
@@ -462,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31A61B23-4538-4B4A-BBC9-0AE8F2E66604}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -500,47 +485,22 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/HGA/filter smh.xlsx
+++ b/HGA/filter smh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD HGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39899060-5C36-4FA7-95F0-C64A637CF2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8345B3-41E7-4E11-9517-11F9F09B06BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA9E0192-5E03-49CC-971F-E04A0DCED2FF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>SMH</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>SCOOPY</t>
+  </si>
+  <si>
+    <t>GENERAL ITEM</t>
   </si>
 </sst>
 </file>
@@ -121,8 +124,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{12048F64-9767-4EC6-B956-9380F61C03FD}" name="FilterSMH" displayName="FilterSMH" ref="A1:A10" totalsRowShown="0">
-  <autoFilter ref="A1:A10" xr:uid="{12048F64-9767-4EC6-B956-9380F61C03FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{12048F64-9767-4EC6-B956-9380F61C03FD}" name="FilterSMH" displayName="FilterSMH" ref="A1:A11" totalsRowShown="0">
+  <autoFilter ref="A1:A11" xr:uid="{12048F64-9767-4EC6-B956-9380F61C03FD}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{1C8D5F6B-37E1-44C6-AAFE-7068A1BAC055}" name="SMH"/>
   </tableColumns>
@@ -447,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31A61B23-4538-4B4A-BBC9-0AE8F2E66604}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -503,6 +506,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
